--- a/filer/10117224_maxizoo.xlsx
+++ b/filer/10117224_maxizoo.xlsx
@@ -615,7 +615,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/10117224_maxizoo.xlsx
+++ b/filer/10117224_maxizoo.xlsx
@@ -595,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -629,7 +629,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -644,35 +644,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1498,35 +1498,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -2976,35 +2976,35 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
@@ -4118,19 +4118,19 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
@@ -4236,19 +4236,19 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
@@ -4546,6 +4546,13 @@
       <c r="F94" s="13">
         <f>IFERROR($F$36/($F$61+0)*100,"")</f>
         <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="15" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse ikke offentliggjort (jf. koncernfritagelse, ÅRL §86, stk. 4)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4577,19 +4584,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -4599,19 +4606,19 @@
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>482375</v>
+        <v>806846</v>
       </c>
       <c r="C2" s="16" t="n">
-        <v>806846</v>
+        <v>839184</v>
       </c>
       <c r="D2" s="16" t="n">
-        <v>839184</v>
+        <v>879860</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>879860</v>
+        <v>898981</v>
       </c>
       <c r="F2" s="16" t="n">
-        <v>898981</v>
+        <v>930685</v>
       </c>
     </row>
     <row r="3">
@@ -4621,19 +4628,19 @@
         </is>
       </c>
       <c r="B3" s="16" t="n">
-        <v>25075</v>
+        <v>45600</v>
       </c>
       <c r="C3" s="16" t="n">
-        <v>45600</v>
+        <v>24575</v>
       </c>
       <c r="D3" s="16" t="n">
-        <v>24575</v>
+        <v>23485</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>23485</v>
+        <v>34362</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>34362</v>
+        <v>11080</v>
       </c>
     </row>
     <row r="4">
@@ -4643,19 +4650,19 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>304027</v>
+        <v>498259</v>
       </c>
       <c r="C4" s="16" t="n">
-        <v>498259</v>
+        <v>509029</v>
       </c>
       <c r="D4" s="16" t="n">
-        <v>509029</v>
+        <v>526670</v>
       </c>
       <c r="E4" s="16" t="n">
-        <v>526670</v>
+        <v>538219</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>538219</v>
+        <v>521066</v>
       </c>
     </row>
     <row r="5">
@@ -4665,19 +4672,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>84070</v>
+        <v>134886</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>134886</v>
+        <v>121365</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>121365</v>
+        <v>135509</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>135509</v>
+        <v>130275</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>130275</v>
+        <v>141007</v>
       </c>
     </row>
     <row r="6">
@@ -4687,19 +4694,19 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>119353</v>
+        <v>219301</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>219301</v>
+        <v>233365</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>233365</v>
+        <v>241166</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>241166</v>
+        <v>264849</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>264849</v>
+        <v>279692</v>
       </c>
     </row>
     <row r="7">
@@ -4709,19 +4716,19 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>96480</v>
+        <v>148834</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>148834</v>
+        <v>153120</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>153120</v>
+        <v>168768</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>168768</v>
+        <v>178921</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>178921</v>
+        <v>187341</v>
       </c>
     </row>
     <row r="8">
@@ -4738,19 +4745,19 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>5835</v>
+        <v>41822</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>41822</v>
+        <v>43170</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>43170</v>
+        <v>45464</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>45464</v>
+        <v>50032</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>50032</v>
+        <v>54021</v>
       </c>
     </row>
     <row r="10">
@@ -4762,9 +4769,11 @@
       <c r="B10" s="16" t="n"/>
       <c r="C10" s="16" t="n"/>
       <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
+      <c r="E10" s="16" t="n">
+        <v>21</v>
+      </c>
       <c r="F10" s="16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4774,19 +4783,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>17038</v>
+        <v>28645</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>28645</v>
+        <v>37075</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>37075</v>
+        <v>26934</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>26934</v>
+        <v>35875</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>35875</v>
+        <v>38330</v>
       </c>
     </row>
     <row r="12">
@@ -4808,19 +4817,19 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>710</v>
+        <v>35</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>35</v>
+        <v>611</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>611</v>
+        <v>4383</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>4383</v>
+        <v>6132</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>6132</v>
+        <v>7514</v>
       </c>
     </row>
     <row r="14">
@@ -4830,19 +4839,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>413</v>
+        <v>1079</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>1079</v>
+        <v>491</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>491</v>
+        <v>539</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>539</v>
+        <v>805</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>805</v>
+        <v>830</v>
       </c>
     </row>
     <row r="15">
@@ -4851,18 +4860,20 @@
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
+      <c r="B15" s="16" t="n">
+        <v>-1044</v>
+      </c>
       <c r="C15" s="16" t="n">
-        <v>-1044</v>
+        <v>120</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>120</v>
+        <v>3844</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>3844</v>
+        <v>5327</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>5327</v>
+        <v>6684</v>
       </c>
     </row>
     <row r="16">
@@ -4872,19 +4883,19 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>17335</v>
+        <v>27601</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>27601</v>
+        <v>37195</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>37195</v>
+        <v>30778</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>30778</v>
+        <v>41202</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>41202</v>
+        <v>45014</v>
       </c>
     </row>
     <row r="17">
@@ -4894,19 +4905,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>1860</v>
+        <v>6265</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>6265</v>
+        <v>7540</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>7540</v>
+        <v>6551</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>6551</v>
+        <v>8944</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>8944</v>
+        <v>9743</v>
       </c>
     </row>
     <row r="18">
@@ -4916,19 +4927,19 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>15475</v>
+        <v>21336</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>21336</v>
+        <v>29655</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>29655</v>
+        <v>24227</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>24227</v>
+        <v>32258</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>32258</v>
+        <v>35271</v>
       </c>
     </row>
     <row r="19">
@@ -4938,19 +4949,19 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>243</v>
+        <v>396</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>396</v>
+        <v>382000</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>382000</v>
+        <v>423000</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>423000</v>
+        <v>432000</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>432000</v>
+        <v>445000</v>
       </c>
     </row>
     <row r="20">
@@ -4960,19 +4971,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>2679</v>
+        <v>41913</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>41913</v>
+        <v>10907</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>10907</v>
+        <v>29844</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>29844</v>
+        <v>29242</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>29242</v>
+        <v>18533</v>
       </c>
     </row>
   </sheetData>
@@ -5004,19 +5015,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -5026,11 +5037,9 @@
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>511</v>
-      </c>
-      <c r="C2" s="16" t="n">
         <v>2204</v>
       </c>
+      <c r="C2" s="16" t="n"/>
       <c r="D2" s="16" t="n"/>
       <c r="E2" s="16" t="n"/>
       <c r="F2" s="16" t="n"/>
@@ -5054,19 +5063,19 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>0</v>
+        <v>265896</v>
       </c>
       <c r="C4" s="16" t="n">
-        <v>265896</v>
+        <v>236342</v>
       </c>
       <c r="D4" s="16" t="n">
-        <v>236342</v>
+        <v>207781</v>
       </c>
       <c r="E4" s="16" t="n">
-        <v>207781</v>
+        <v>178147</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>178147</v>
+        <v>148503</v>
       </c>
     </row>
     <row r="5">
@@ -5076,18 +5085,20 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>511</v>
+        <v>268100</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>268100</v>
+        <v>240965</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>240965</v>
+        <v>211875</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>211875</v>
-      </c>
-      <c r="F5" s="16" t="n"/>
+        <v>180536</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>152609</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
@@ -5120,19 +5131,19 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>9265</v>
+        <v>40872</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>40872</v>
+        <v>33568</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>33568</v>
+        <v>32098</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>32098</v>
+        <v>33711</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>33711</v>
+        <v>29904</v>
       </c>
     </row>
     <row r="9">
@@ -5142,15 +5153,17 @@
         </is>
       </c>
       <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
+      <c r="C9" s="16" t="n">
+        <v>5310</v>
+      </c>
       <c r="D9" s="16" t="n">
-        <v>5310</v>
+        <v>22419</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>22419</v>
+        <v>31216</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>31216</v>
+        <v>30523</v>
       </c>
     </row>
     <row r="10">
@@ -5172,14 +5185,18 @@
         </is>
       </c>
       <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
+      <c r="C11" s="16" t="n">
+        <v>38878</v>
+      </c>
       <c r="D11" s="16" t="n">
-        <v>38878</v>
+        <v>54517</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>54517</v>
-      </c>
-      <c r="F11" s="16" t="n"/>
+        <v>64927</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>60427</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
@@ -5200,19 +5217,19 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>9535</v>
+        <v>9354</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>9354</v>
+        <v>8789</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>8789</v>
+        <v>8507</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>8507</v>
+        <v>8745</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>8745</v>
+        <v>8927</v>
       </c>
     </row>
     <row r="14">
@@ -5234,19 +5251,19 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>19311</v>
+        <v>318326</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>318326</v>
+        <v>288632</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>288632</v>
+        <v>274899</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>274899</v>
+        <v>254208</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>254208</v>
+        <v>221963</v>
       </c>
     </row>
     <row r="16">
@@ -5280,19 +5297,19 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>50994</v>
+        <v>83987</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>83987</v>
+        <v>96871</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>96871</v>
+        <v>95306</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>95306</v>
+        <v>97801</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>97801</v>
+        <v>113315</v>
       </c>
     </row>
     <row r="19">
@@ -5302,19 +5319,19 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>50994</v>
+        <v>83987</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>83987</v>
+        <v>96871</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>96871</v>
+        <v>95306</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>95306</v>
+        <v>97801</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>97801</v>
+        <v>113315</v>
       </c>
     </row>
     <row r="20">
@@ -5324,19 +5341,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>5200</v>
+        <v>8472</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>8472</v>
+        <v>19517</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>19517</v>
+        <v>18500</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>18500</v>
+        <v>15271</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>15271</v>
+        <v>20393</v>
       </c>
     </row>
     <row r="21">
@@ -5346,19 +5363,19 @@
         </is>
       </c>
       <c r="B21" s="16" t="n">
-        <v>0</v>
+        <v>35251</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>35251</v>
+        <v>45000</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>45000</v>
+        <v>85000</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>85000</v>
+        <v>145110</v>
       </c>
       <c r="F21" s="16" t="n">
-        <v>145110</v>
+        <v>181194</v>
       </c>
     </row>
     <row r="22">
@@ -5368,19 +5385,19 @@
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>58768</v>
+        <v>12154</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>12154</v>
+        <v>11212</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>11212</v>
+        <v>8296</v>
       </c>
       <c r="E22" s="16" t="n">
-        <v>8296</v>
+        <v>8577</v>
       </c>
       <c r="F22" s="16" t="n">
-        <v>8577</v>
+        <v>11781</v>
       </c>
     </row>
     <row r="23">
@@ -5390,19 +5407,19 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>2829</v>
+        <v>3937</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>3937</v>
+        <v>2715</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>2715</v>
+        <v>2480</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>2480</v>
+        <v>3256</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>3256</v>
+        <v>3395</v>
       </c>
     </row>
     <row r="24">
@@ -5412,11 +5429,9 @@
         </is>
       </c>
       <c r="B24" s="16" t="n">
-        <v>1932</v>
-      </c>
-      <c r="C24" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="C24" s="16" t="n"/>
       <c r="D24" s="16" t="n"/>
       <c r="E24" s="16" t="n"/>
       <c r="F24" s="16" t="n"/>
@@ -5440,11 +5455,9 @@
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>427</v>
-      </c>
-      <c r="C26" s="16" t="n">
         <v>110</v>
       </c>
+      <c r="C26" s="16" t="n"/>
       <c r="D26" s="16" t="n"/>
       <c r="E26" s="16" t="n"/>
       <c r="F26" s="16" t="n"/>
@@ -5456,18 +5469,20 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>69156</v>
+        <v>59924</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>59924</v>
+        <v>78444</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>78444</v>
+        <v>114276</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>114276</v>
-      </c>
-      <c r="F27" s="16" t="n"/>
+        <v>172214</v>
+      </c>
+      <c r="F27" s="16" t="n">
+        <v>216763</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
@@ -5488,19 +5503,19 @@
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>333617</v>
+        <v>59738</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>59738</v>
+        <v>68278</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>68278</v>
+        <v>74238</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>74238</v>
+        <v>60985</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>60985</v>
+        <v>47225</v>
       </c>
     </row>
     <row r="30">
@@ -5510,19 +5525,19 @@
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>453767</v>
+        <v>203649</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>203649</v>
+        <v>243593</v>
       </c>
       <c r="D30" s="16" t="n">
-        <v>243593</v>
+        <v>283820</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>283820</v>
+        <v>331000</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>331000</v>
+        <v>377303</v>
       </c>
     </row>
     <row r="31">
@@ -5532,19 +5547,19 @@
         </is>
       </c>
       <c r="B31" s="16" t="n">
-        <v>473078</v>
+        <v>521975</v>
       </c>
       <c r="C31" s="16" t="n">
-        <v>521975</v>
+        <v>532225</v>
       </c>
       <c r="D31" s="16" t="n">
-        <v>532225</v>
+        <v>558719</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>558719</v>
+        <v>585208</v>
       </c>
       <c r="F31" s="16" t="n">
-        <v>585208</v>
+        <v>599266</v>
       </c>
     </row>
     <row r="32">
@@ -5624,19 +5639,19 @@
         </is>
       </c>
       <c r="B37" s="16" t="n">
-        <v>402920</v>
+        <v>410956</v>
       </c>
       <c r="C37" s="16" t="n">
-        <v>410956</v>
+        <v>440611</v>
       </c>
       <c r="D37" s="16" t="n">
-        <v>440611</v>
+        <v>464838</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>464838</v>
+        <v>468096</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>468096</v>
+        <v>464367</v>
       </c>
     </row>
     <row r="38">
@@ -5646,19 +5661,19 @@
         </is>
       </c>
       <c r="B38" s="16" t="n">
-        <v>403970</v>
+        <v>425306</v>
       </c>
       <c r="C38" s="16" t="n">
-        <v>425306</v>
+        <v>441661</v>
       </c>
       <c r="D38" s="16" t="n">
-        <v>441661</v>
+        <v>465888</v>
       </c>
       <c r="E38" s="16" t="n">
-        <v>465888</v>
+        <v>498146</v>
       </c>
       <c r="F38" s="16" t="n">
-        <v>498146</v>
+        <v>504417</v>
       </c>
     </row>
     <row r="39">
@@ -5668,15 +5683,17 @@
         </is>
       </c>
       <c r="B39" s="16" t="n"/>
-      <c r="C39" s="16" t="n"/>
+      <c r="C39" s="16" t="n">
+        <v>4496</v>
+      </c>
       <c r="D39" s="16" t="n">
-        <v>4496</v>
+        <v>6943</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>6943</v>
+        <v>11750</v>
       </c>
       <c r="F39" s="16" t="n">
-        <v>11750</v>
+        <v>11558</v>
       </c>
     </row>
     <row r="40">
@@ -5686,19 +5703,19 @@
         </is>
       </c>
       <c r="B40" s="16" t="n">
-        <v>4867</v>
+        <v>3158</v>
       </c>
       <c r="C40" s="16" t="n">
-        <v>3158</v>
+        <v>4496</v>
       </c>
       <c r="D40" s="16" t="n">
-        <v>4496</v>
+        <v>6943</v>
       </c>
       <c r="E40" s="16" t="n">
-        <v>6943</v>
+        <v>20234</v>
       </c>
       <c r="F40" s="16" t="n">
-        <v>20234</v>
+        <v>20756</v>
       </c>
     </row>
     <row r="41">
@@ -5756,19 +5773,19 @@
         </is>
       </c>
       <c r="B45" s="16" t="n">
-        <v>29958</v>
+        <v>38972</v>
       </c>
       <c r="C45" s="16" t="n">
-        <v>38972</v>
+        <v>33231</v>
       </c>
       <c r="D45" s="16" t="n">
-        <v>33231</v>
+        <v>36633</v>
       </c>
       <c r="E45" s="16" t="n">
-        <v>36633</v>
+        <v>12883</v>
       </c>
       <c r="F45" s="16" t="n">
-        <v>12883</v>
+        <v>28547</v>
       </c>
     </row>
     <row r="46">
@@ -5780,9 +5797,11 @@
       <c r="B46" s="16" t="n"/>
       <c r="C46" s="16" t="n"/>
       <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
+      <c r="E46" s="16" t="n">
+        <v>16501</v>
+      </c>
       <c r="F46" s="16" t="n">
-        <v>16501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -5804,15 +5823,17 @@
         </is>
       </c>
       <c r="B48" s="16" t="n"/>
-      <c r="C48" s="16" t="n"/>
+      <c r="C48" s="16" t="n">
+        <v>4024</v>
+      </c>
       <c r="D48" s="16" t="n">
-        <v>4024</v>
+        <v>3063</v>
       </c>
       <c r="E48" s="16" t="n">
-        <v>3063</v>
+        <v>2544</v>
       </c>
       <c r="F48" s="16" t="n">
-        <v>2544</v>
+        <v>8094</v>
       </c>
     </row>
     <row r="49">
@@ -5834,19 +5855,19 @@
         </is>
       </c>
       <c r="B50" s="16" t="n">
-        <v>31647</v>
+        <v>38316</v>
       </c>
       <c r="C50" s="16" t="n">
-        <v>38316</v>
+        <v>35252</v>
       </c>
       <c r="D50" s="16" t="n">
-        <v>35252</v>
+        <v>32411</v>
       </c>
       <c r="E50" s="16" t="n">
-        <v>32411</v>
+        <v>29553</v>
       </c>
       <c r="F50" s="16" t="n">
-        <v>29553</v>
+        <v>31615</v>
       </c>
     </row>
     <row r="51">
@@ -5856,19 +5877,19 @@
         </is>
       </c>
       <c r="B51" s="16" t="n">
-        <v>2636</v>
+        <v>16223</v>
       </c>
       <c r="C51" s="16" t="n">
-        <v>16223</v>
+        <v>13561</v>
       </c>
       <c r="D51" s="16" t="n">
-        <v>13561</v>
+        <v>13781</v>
       </c>
       <c r="E51" s="16" t="n">
-        <v>13781</v>
+        <v>5347</v>
       </c>
       <c r="F51" s="16" t="n">
-        <v>5347</v>
+        <v>5837</v>
       </c>
     </row>
     <row r="52">
@@ -5878,19 +5899,19 @@
         </is>
       </c>
       <c r="B52" s="16" t="n">
-        <v>64241</v>
+        <v>93511</v>
       </c>
       <c r="C52" s="16" t="n">
-        <v>93511</v>
+        <v>86068</v>
       </c>
       <c r="D52" s="16" t="n">
-        <v>86068</v>
+        <v>85888</v>
       </c>
       <c r="E52" s="16" t="n">
-        <v>85888</v>
+        <v>66828</v>
       </c>
       <c r="F52" s="16" t="n">
-        <v>66828</v>
+        <v>74093</v>
       </c>
     </row>
     <row r="53">
@@ -5900,19 +5921,19 @@
         </is>
       </c>
       <c r="B53" s="16" t="n">
-        <v>64241</v>
+        <v>93511</v>
       </c>
       <c r="C53" s="16" t="n">
-        <v>93511</v>
+        <v>86068</v>
       </c>
       <c r="D53" s="16" t="n">
-        <v>86068</v>
+        <v>85888</v>
       </c>
       <c r="E53" s="16" t="n">
-        <v>85888</v>
+        <v>66828</v>
       </c>
       <c r="F53" s="16" t="n">
-        <v>66828</v>
+        <v>74093</v>
       </c>
     </row>
     <row r="54">
@@ -5922,19 +5943,19 @@
         </is>
       </c>
       <c r="B54" s="16" t="n">
-        <v>473078</v>
+        <v>521975</v>
       </c>
       <c r="C54" s="16" t="n">
-        <v>521975</v>
+        <v>532225</v>
       </c>
       <c r="D54" s="16" t="n">
-        <v>532225</v>
+        <v>558719</v>
       </c>
       <c r="E54" s="16" t="n">
-        <v>558719</v>
+        <v>585208</v>
       </c>
       <c r="F54" s="16" t="n">
-        <v>585208</v>
+        <v>599266</v>
       </c>
     </row>
   </sheetData>
@@ -5973,13 +5994,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -6693,7 +6714,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -6811,7 +6832,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -6987,7 +7008,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
